--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484352_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484352_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4169</v>
+        <v>6.9622</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0762</v>
+        <v>4.946</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3407</v>
+        <v>2.0162</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6247</v>
+        <v>4.0856</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9911</v>
+        <v>3.5191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5665</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5931</v>
+        <v>4.1054</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8243</v>
+        <v>3.4037</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7688</v>
+        <v>0.7017</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9684</v>
+        <v>-0.0198</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.1154</v>
       </c>
       <c r="O2" t="n">
         <v>-0.1352</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9534</v>
+        <v>2.9301</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>2.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>1.675</v>
+        <v>0.5558</v>
       </c>
       <c r="T2" t="n">
-        <v>1.296</v>
+        <v>0.2312</v>
       </c>
       <c r="U2" t="n">
-        <v>0.379</v>
+        <v>0.3245</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1638</v>
+        <v>-0.6093</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1638</v>
+        <v>0.6093</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6001</v>
+        <v>6.4428</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4204</v>
+        <v>4.4289</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1796</v>
+        <v>2.0139</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0856</v>
+        <v>2.6247</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5191</v>
+        <v>1.9911</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5665</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1054</v>
+        <v>3.5931</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4037</v>
+        <v>2.8243</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7017</v>
+        <v>0.7688</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0198</v>
+        <v>-0.9684</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1154</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>-0.1352</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9301</v>
+        <v>1.9534</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
         <v>2.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1937</v>
+        <v>0.7009</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2943</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4879</v>
+        <v>0.0522</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6093</v>
+        <v>1.1638</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6093</v>
+        <v>1.1638</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4839</v>
+        <v>4.6363</v>
       </c>
       <c r="E4" t="n">
-        <v>4.375</v>
+        <v>1.4259</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1089</v>
+        <v>3.2104</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3026</v>
+        <v>2.6939</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3993</v>
+        <v>2.3692</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9033</v>
+        <v>0.3247</v>
       </c>
       <c r="J4" t="n">
-        <v>4.271</v>
+        <v>2.9184</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5022</v>
+        <v>2.4584</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7688</v>
+        <v>0.4599</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9684</v>
+        <v>-0.2245</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1028</v>
+        <v>-0.0893</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1344</v>
+        <v>-0.1352</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>2.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2948</v>
+        <v>0.6885</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8035</v>
+        <v>0.1838</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4913</v>
+        <v>0.5047</v>
       </c>
       <c r="V4" t="n">
         <v>0.2772</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3511</v>
+        <v>4.4195</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5905</v>
+        <v>4.5499</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2393</v>
+        <v>-0.1304</v>
       </c>
       <c r="G5" t="n">
         <v>2.2137</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.356</v>
+        <v>0.4244</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1899</v>
+        <v>0.1493</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1661</v>
+        <v>0.2751</v>
       </c>
       <c r="V5" t="n">
         <v>0.6093</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7414</v>
+        <v>3.8288</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3948</v>
+        <v>3.8289</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3466</v>
+        <v>-0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6939</v>
+        <v>3.3026</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3692</v>
+        <v>2.3993</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3247</v>
+        <v>0.9033</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9184</v>
+        <v>4.271</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4584</v>
+        <v>3.5022</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4599</v>
+        <v>0.7688</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2245</v>
+        <v>-0.9684</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0893</v>
+        <v>-1.1028</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1352</v>
+        <v>0.1344</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9301</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2064</v>
+        <v>0.6397</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.2573</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6409</v>
+        <v>0.3823</v>
       </c>
       <c r="V6" t="n">
         <v>0.2772</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3714</v>
+        <v>1.5865</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1998</v>
+        <v>1.0271</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8283</v>
+        <v>0.5594</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9887</v>
+        <v>1.8548</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0558</v>
+        <v>0.7222</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06710000000000001</v>
+        <v>1.1326</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0735</v>
+        <v>1.8745</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0054</v>
+        <v>1.1461</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.7284</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0848</v>
+        <v>-0.0196</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0504</v>
+        <v>-0.4239</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1352</v>
+        <v>0.4043</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3441</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4759</v>
+        <v>0.6768</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8491</v>
+        <v>0.1294</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3732</v>
+        <v>0.5474</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2536</v>
+        <v>1.3275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9666</v>
+        <v>2.0469</v>
       </c>
       <c r="F8" t="n">
-        <v>0.287</v>
+        <v>-0.7194</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8548</v>
+        <v>0.9887</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7222</v>
+        <v>1.0558</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1326</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8745</v>
+        <v>1.0735</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1461</v>
+        <v>1.0054</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7284</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0196</v>
+        <v>-0.0848</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4239</v>
+        <v>0.0504</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4043</v>
+        <v>-0.1352</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3439</v>
+        <v>0.432</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0689</v>
+        <v>0.6962</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2751</v>
+        <v>-0.2642</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5545</v>
+        <v>-2.4373</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2485</v>
+        <v>0.4646</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4873</v>
+        <v>-0.3256</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7358</v>
+        <v>0.7903</v>
       </c>
       <c r="G9" t="n">
         <v>0.3684</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1574</v>
+        <v>0.3735</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1816</v>
+        <v>-0.0199</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3389</v>
+        <v>0.3934</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2772</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1273</v>
+        <v>0.1549</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.71</v>
+        <v>-0.3461</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5827</v>
+        <v>0.501</v>
       </c>
       <c r="G10" t="n">
         <v>1.3687</v>
@@ -1234,13 +1234,13 @@
         <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4727</v>
+        <v>-0.1905</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5447</v>
+        <v>-0.1808</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.0097</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4742</v>
+        <v>-0.1454</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6348</v>
+        <v>-0.1698</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1606</v>
+        <v>0.0244</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7328</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3275</v>
+        <v>0.0014</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6657</v>
+        <v>-0.2008</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3383</v>
+        <v>0.2021</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.737</v>
+        <v>-1.2425</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6687</v>
+        <v>-1.4466</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0683</v>
+        <v>0.204</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6732</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0413</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1294</v>
+        <v>0.3516</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0881</v>
+        <v>0.1843</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8865</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6893</v>
+        <v>-2.0881</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3536</v>
+        <v>-1.8886</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3357</v>
+        <v>-0.1995</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4656</v>
@@ -1468,13 +1468,13 @@
         <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5558</v>
+        <v>0.0454</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6052</v>
+        <v>-0.1402</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0495</v>
+        <v>0.1856</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2772</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.4391</v>
+        <v>26.3471</v>
       </c>
       <c r="E14" t="n">
-        <v>17.1689</v>
+        <v>18.0769</v>
       </c>
       <c r="F14" t="n">
         <v>8.270300000000001</v>
@@ -1531,10 +1531,10 @@
         <v>-4.9411</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.937200000000001</v>
+        <v>-4.9372</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.003899999999999948</v>
+        <v>-0.003899999999999976</v>
       </c>
       <c r="P14" t="n">
         <v>9.766999999999998</v>
@@ -1546,10 +1546,10 @@
         <v>17.5807</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9756</v>
+        <v>4.8837</v>
       </c>
       <c r="T14" t="n">
-        <v>1.198</v>
+        <v>2.105799999999999</v>
       </c>
       <c r="U14" t="n">
         <v>2.7777</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.034</v>
+        <v>-0.2538</v>
       </c>
       <c r="E15" t="n">
-        <v>1.275</v>
+        <v>0.7883</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3089</v>
+        <v>-1.0421</v>
       </c>
       <c r="G15" t="n">
-        <v>0.112</v>
+        <v>-0.4698</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7391</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8897</v>
+        <v>0.2692</v>
       </c>
       <c r="J15" t="n">
-        <v>1.685</v>
+        <v>1.3123</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3901</v>
+        <v>1.3123</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2949</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5731</v>
+        <v>-1.7822</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1678</v>
+        <v>-2.0514</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4052</v>
+        <v>0.2692</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4754</v>
+        <v>-0.37</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3247</v>
+        <v>-0.524</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1507</v>
+        <v>0.154</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.2907</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2584</v>
+        <v>1.0727</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.776</v>
+        <v>-1.3634</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2117</v>
+        <v>0.112</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5431</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7548</v>
+        <v>0.8897</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7247</v>
+        <v>1.685</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4298</v>
+        <v>0.3901</v>
       </c>
       <c r="L16" t="n">
         <v>1.2949</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5129</v>
+        <v>-1.5731</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9729</v>
+        <v>-1.1678</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5401</v>
+        <v>-0.4052</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3674</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>0.306</v>
+        <v>0.2187</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6824</v>
+        <v>0.1225</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3765</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3321</v>
+        <v>0.9414</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.6703</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5861</v>
+        <v>1.2268</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.26</v>
+        <v>-1.8971</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4698</v>
+        <v>0.2021</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7391</v>
+        <v>0.7958</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2692</v>
+        <v>-0.5938</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3123</v>
+        <v>2.7339</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3123</v>
+        <v>2.7871</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7822</v>
+        <v>-2.5318</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0514</v>
+        <v>-1.9913</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2692</v>
+        <v>-0.5405</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7901</v>
+        <v>-0.8371</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.7723</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0639</v>
+        <v>-0.0648</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.783</v>
+        <v>-0.9687</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9234</v>
+        <v>-0.2472</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7064</v>
+        <v>-0.7215</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2021</v>
+        <v>0.2117</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7958</v>
+        <v>-0.5431</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5938</v>
+        <v>0.7548</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7339</v>
+        <v>1.7247</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7871</v>
+        <v>0.4298</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0533</v>
+        <v>1.2949</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5318</v>
+        <v>-1.5129</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9913</v>
+        <v>-0.9729</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5405</v>
+        <v>-0.5401</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9498</v>
+        <v>-0.1452</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0756</v>
+        <v>0.1769</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1258</v>
+        <v>-0.322</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2945</v>
+        <v>-1.9836</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1408</v>
+        <v>0.4783</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1537</v>
+        <v>-2.4619</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0228</v>
+        <v>-0.8527</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0806</v>
+        <v>-0.4346</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9422</v>
+        <v>-0.4181</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0355</v>
+        <v>1.2791</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9059</v>
+        <v>1.2919</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9414</v>
+        <v>-0.0128</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9872</v>
+        <v>-2.1318</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9864</v>
+        <v>-1.7265</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0008</v>
+        <v>-0.4052</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R19" t="n">
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9629</v>
+        <v>-0.3728</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0151</v>
+        <v>0.1294</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0522</v>
+        <v>-0.5022</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8865</v>
+        <v>0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8865</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3377</v>
+        <v>-2.0923</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4783</v>
+        <v>-0.9386</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.816</v>
+        <v>-1.1537</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8527</v>
+        <v>-2.0228</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4346</v>
+        <v>-0.0806</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4181</v>
+        <v>-1.9422</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2791</v>
+        <v>-0.0355</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2919</v>
+        <v>1.9059</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0128</v>
+        <v>-1.9414</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1318</v>
+        <v>-1.9872</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7265</v>
+        <v>-1.9864</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4052</v>
+        <v>-0.0008</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7269</v>
+        <v>-0.7607</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1294</v>
+        <v>-0.8129</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8563</v>
+        <v>0.0522</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6093</v>
+        <v>0.8865</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4387</v>
+        <v>-2.3103</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7683</v>
+        <v>-1.6672</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6703</v>
+        <v>-0.6431</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8784</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4468</v>
+        <v>-0.3185</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0837</v>
+        <v>-0.0565</v>
       </c>
       <c r="V21" t="n">
         <v>0.2772</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5304</v>
+        <v>-3.1023</v>
       </c>
       <c r="E22" t="n">
         <v>-2.1472</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3832</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-4.7887</v>
@@ -2170,13 +2170,13 @@
         <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2899</v>
+        <v>-0.2821</v>
       </c>
       <c r="T22" t="n">
         <v>-0.5831</v>
       </c>
       <c r="U22" t="n">
-        <v>0.873</v>
+        <v>0.301</v>
       </c>
       <c r="V22" t="n">
         <v>1.7731</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4959</v>
+        <v>-6.4765</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5438</v>
+        <v>-2.4426</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9521</v>
+        <v>-4.0338</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7768</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1563</v>
+        <v>-0.1369</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0083</v>
+        <v>0.1095</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1647</v>
+        <v>-0.2464</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2186</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.3337</v>
+        <v>-7.2908</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1913</v>
+        <v>-4.3935</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1424</v>
+        <v>-2.8973</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3662</v>
@@ -2326,13 +2326,13 @@
         <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0141</v>
+        <v>-0.9712</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1594</v>
+        <v>-0.3617</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8546</v>
+        <v>-0.6095</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6093</v>
@@ -2359,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-25.4394</v>
+        <v>-25.4393</v>
       </c>
       <c r="E25" t="n">
         <v>-8.270200000000001</v>
@@ -2383,7 +2383,7 @@
         <v>4.937099999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003899999999999904</v>
+        <v>0.003900000000000348</v>
       </c>
       <c r="M25" t="n">
         <v>-20.5707</v>
@@ -2404,10 +2404,10 @@
         <v>7.8138</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.9756</v>
+        <v>-3.9758</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.777799999999999</v>
+        <v>-2.7777</v>
       </c>
       <c r="U25" t="n">
         <v>-1.198</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484352_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484352_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6363</v>
+        <v>4.4195</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4259</v>
+        <v>4.5499</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2104</v>
+        <v>-0.1304</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6939</v>
+        <v>2.2137</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3692</v>
+        <v>0.8788</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3247</v>
+        <v>1.335</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9184</v>
+        <v>3.7913</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4584</v>
+        <v>2.4559</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4599</v>
+        <v>1.3354</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2245</v>
+        <v>-1.5775</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0893</v>
+        <v>-1.5771</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1352</v>
+        <v>-0.0004</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9301</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6885</v>
+        <v>0.4244</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1838</v>
+        <v>0.1493</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5047</v>
+        <v>0.2751</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4195</v>
+        <v>3.8288</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5499</v>
+        <v>3.8289</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1304</v>
+        <v>-0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2137</v>
+        <v>3.3026</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8788</v>
+        <v>2.3993</v>
       </c>
       <c r="I5" t="n">
-        <v>1.335</v>
+        <v>0.9033</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7913</v>
+        <v>4.271</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4559</v>
+        <v>3.5022</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3354</v>
+        <v>0.7688</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5775</v>
+        <v>-0.9684</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5771</v>
+        <v>-1.1028</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0004</v>
+        <v>0.1344</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4244</v>
+        <v>0.6397</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1493</v>
+        <v>0.2573</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2751</v>
+        <v>0.3823</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +902,72 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8288</v>
+        <v>3.6699</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8289</v>
+        <v>3.6699</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3026</v>
+        <v>3.6699</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3993</v>
+        <v>2.4559</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9033</v>
+        <v>1.214</v>
       </c>
       <c r="J6" t="n">
-        <v>4.271</v>
+        <v>3.6699</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5022</v>
+        <v>2.4559</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7688</v>
+        <v>1.214</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9684</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1028</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6397</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2573</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3823</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. BAYO GARCIA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4646</v>
+        <v>0.9665</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3256</v>
+        <v>-2.2439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7903</v>
+        <v>3.2104</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3684</v>
+        <v>-0.976</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9077</v>
+        <v>-0.0867</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5393</v>
+        <v>-0.8893</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3057</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3684</v>
+        <v>0.0025</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6741</v>
+        <v>-0.754</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6741</v>
+        <v>-0.2245</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5393</v>
+        <v>-0.0893</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1348</v>
+        <v>-0.1352</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3735</v>
+        <v>0.6885</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0199</v>
+        <v>0.1838</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3934</v>
+        <v>0.5047</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>G. BAYO GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1549</v>
+        <v>0.4646</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3461</v>
+        <v>-0.3256</v>
       </c>
       <c r="F10" t="n">
-        <v>0.501</v>
+        <v>0.7903</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3687</v>
+        <v>0.3684</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1686</v>
+        <v>0.9077</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2002</v>
+        <v>-0.5393</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7882</v>
+        <v>-0.3057</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4528</v>
+        <v>0.3684</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3354</v>
+        <v>-0.6741</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4194</v>
+        <v>0.6741</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2842</v>
+        <v>0.5393</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1352</v>
+        <v>0.1348</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1905</v>
+        <v>0.3735</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1808</v>
+        <v>-0.0199</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0097</v>
+        <v>0.3934</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1454</v>
+        <v>0.1549</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1698</v>
+        <v>-0.3461</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0244</v>
+        <v>0.501</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7328</v>
+        <v>1.3687</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4129</v>
+        <v>0.1686</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1457</v>
+        <v>1.2002</v>
       </c>
       <c r="J11" t="n">
-        <v>0.031</v>
+        <v>1.7882</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3111</v>
+        <v>0.4528</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2801</v>
+        <v>1.3354</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7638</v>
+        <v>-0.4194</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8982</v>
+        <v>-0.2842</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1344</v>
+        <v>-0.1352</v>
       </c>
       <c r="P11" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0014</v>
+        <v>-0.1905</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2008</v>
+        <v>-0.1808</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2021</v>
+        <v>-0.0097</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2425</v>
+        <v>-0.1454</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4466</v>
+        <v>-0.1698</v>
       </c>
       <c r="F12" t="n">
-        <v>0.204</v>
+        <v>0.0244</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6732</v>
+        <v>-0.7328</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4032</v>
+        <v>0.4129</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0764</v>
+        <v>-1.1457</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7981</v>
+        <v>0.031</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1433</v>
+        <v>1.3111</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9414</v>
+        <v>-1.2801</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1249</v>
+        <v>-0.7638</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2599</v>
+        <v>-0.8982</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.135</v>
+        <v>0.1344</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.0014</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3516</v>
+        <v>-0.2008</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1843</v>
+        <v>0.2021</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0881</v>
+        <v>-1.2425</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8886</v>
+        <v>-1.4466</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1995</v>
+        <v>0.204</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4656</v>
+        <v>-1.6732</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8985</v>
+        <v>0.4032</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4329</v>
+        <v>-2.0764</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-1.7981</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2049</v>
+        <v>0.1433</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4333</v>
+        <v>-1.9414</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6939</v>
+        <v>0.1249</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6935</v>
+        <v>0.2599</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0004</v>
+        <v>-0.135</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0454</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1402</v>
+        <v>0.3516</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1856</v>
+        <v>0.1843</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,146 +1566,152 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.3471</v>
+        <v>-2.0881</v>
       </c>
       <c r="E14" t="n">
-        <v>18.0769</v>
+        <v>-1.8886</v>
       </c>
       <c r="F14" t="n">
-        <v>8.270300000000001</v>
+        <v>-0.1995</v>
       </c>
       <c r="G14" t="n">
-        <v>15.6295</v>
+        <v>-1.4656</v>
       </c>
       <c r="H14" t="n">
-        <v>12.9294</v>
+        <v>-1.8985</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7003</v>
+        <v>0.4329</v>
       </c>
       <c r="J14" t="n">
-        <v>20.5709</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>17.8667</v>
+        <v>-1.2049</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7042</v>
+        <v>0.4333</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.9411</v>
+        <v>-0.6939</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.9372</v>
+        <v>-0.6935</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.003899999999999976</v>
+        <v>-0.0004</v>
       </c>
       <c r="P14" t="n">
-        <v>9.766999999999998</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.8136</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>17.5807</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8837</v>
+        <v>0.0454</v>
       </c>
       <c r="T14" t="n">
-        <v>2.105799999999999</v>
+        <v>-0.1402</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7777</v>
+        <v>0.1856</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.9331</v>
+        <v>-0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>3.214</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.147099999999999</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2538</v>
+        <v>26.3472</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7883</v>
+        <v>18.077</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0421</v>
+        <v>8.270300000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4698</v>
+        <v>15.6295</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7391</v>
+        <v>12.9294</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2692</v>
+        <v>2.7003</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3123</v>
+        <v>20.5709</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3123</v>
+        <v>17.8667</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.7043</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7822</v>
+        <v>-4.9411</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0514</v>
+        <v>-4.937200000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2692</v>
+        <v>-0.003899999999999976</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>9.766999999999998</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-7.8136</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>17.5807</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.37</v>
+        <v>4.8837</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.524</v>
+        <v>2.1058</v>
       </c>
       <c r="U15" t="n">
-        <v>0.154</v>
+        <v>2.7777</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-3.9331</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.214</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-7.147099999999999</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2907</v>
+        <v>2.1349</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0727</v>
+        <v>2.1349</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3634</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.112</v>
+        <v>2.1349</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7776999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8897</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>1.685</v>
+        <v>2.1349</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3901</v>
+        <v>0.921</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2949</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5731</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1678</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4052</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2187</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1225</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09619999999999999</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6703</v>
+        <v>-0.2538</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2268</v>
+        <v>0.7883</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8971</v>
+        <v>-1.0421</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2021</v>
+        <v>-0.4698</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7958</v>
+        <v>-0.7391</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5938</v>
+        <v>0.2692</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7339</v>
+        <v>1.3123</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7871</v>
+        <v>1.3123</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5318</v>
+        <v>-1.7822</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9913</v>
+        <v>-2.0514</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5405</v>
+        <v>0.2692</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8371</v>
+        <v>-0.37</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7723</v>
+        <v>-0.524</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0648</v>
+        <v>0.154</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9687</v>
+        <v>-0.6703</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2472</v>
+        <v>1.2268</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7215</v>
+        <v>-1.8971</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2117</v>
+        <v>0.2021</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5431</v>
+        <v>0.7958</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7548</v>
+        <v>-0.5938</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7247</v>
+        <v>2.7339</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4298</v>
+        <v>2.7871</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2949</v>
+        <v>-0.0533</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5129</v>
+        <v>-2.5318</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9729</v>
+        <v>-1.9913</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5401</v>
+        <v>-0.5405</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1452</v>
+        <v>-0.8371</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1769</v>
+        <v>-0.7723</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.322</v>
+        <v>-0.0648</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1977,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9836</v>
+        <v>-0.9687</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4783</v>
+        <v>-0.2472</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4619</v>
+        <v>-0.7215</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8527</v>
+        <v>0.2117</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4346</v>
+        <v>-0.5431</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4181</v>
+        <v>0.7548</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2791</v>
+        <v>1.7247</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2919</v>
+        <v>0.4298</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0128</v>
+        <v>1.2949</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1318</v>
+        <v>-1.5129</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7265</v>
+        <v>-0.9729</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4052</v>
+        <v>-0.5401</v>
       </c>
       <c r="P19" t="n">
         <v>-1.3674</v>
@@ -1936,28 +2022,33 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3728</v>
+        <v>-0.1452</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1294</v>
+        <v>0.1769</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5022</v>
+        <v>-0.322</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6093</v>
+        <v>0.3321</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0923</v>
+        <v>-1.9836</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9386</v>
+        <v>0.4783</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1537</v>
+        <v>-2.4619</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0228</v>
+        <v>-0.8527</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0806</v>
+        <v>-0.4346</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9422</v>
+        <v>-0.4181</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0355</v>
+        <v>1.2791</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9059</v>
+        <v>1.2919</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9414</v>
+        <v>-0.0128</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9872</v>
+        <v>-2.1318</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9864</v>
+        <v>-1.7265</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0008</v>
+        <v>-0.4052</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7607</v>
+        <v>-0.3728</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8129</v>
+        <v>0.1294</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0522</v>
+        <v>-0.5022</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8865</v>
+        <v>0.6093</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8865</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3103</v>
+        <v>-2.0923</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6672</v>
+        <v>-0.9386</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6431</v>
+        <v>-1.1537</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8784</v>
+        <v>-2.0228</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3387</v>
+        <v>-0.0806</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5397</v>
+        <v>-1.9422</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5104</v>
+        <v>-0.0355</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5104</v>
+        <v>1.9059</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.9414</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.368</v>
+        <v>-1.9872</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8283</v>
+        <v>-1.9864</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5397</v>
+        <v>-0.0008</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3185</v>
+        <v>-0.7607</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.262</v>
+        <v>-0.8129</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0565</v>
+        <v>0.0522</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1023</v>
+        <v>-2.3103</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1472</v>
+        <v>-1.6672</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.6431</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.7887</v>
+        <v>-1.8784</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.2198</v>
+        <v>-1.3387</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4311</v>
+        <v>-0.5397</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4424</v>
+        <v>-0.5104</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.47</v>
+        <v>-0.5104</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0276</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3463</v>
+        <v>-1.368</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.7498</v>
+        <v>-0.8283</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4035</v>
+        <v>-0.5397</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2821</v>
+        <v>-0.3185</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5831</v>
+        <v>-0.262</v>
       </c>
       <c r="U22" t="n">
-        <v>0.301</v>
+        <v>-0.0565</v>
       </c>
       <c r="V22" t="n">
-        <v>1.7731</v>
+        <v>0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>2.0503</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4765</v>
+        <v>-2.4256</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4426</v>
+        <v>-1.0622</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0338</v>
+        <v>-1.3634</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7768</v>
+        <v>-2.023</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.913</v>
+        <v>-1.6987</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8638</v>
+        <v>-0.3243</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5734</v>
+        <v>-0.4499</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4924</v>
+        <v>-0.5308</v>
       </c>
       <c r="L23" t="n">
         <v>0.0809</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3502</v>
+        <v>-1.5731</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.4055</v>
+        <v>-1.1678</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9447</v>
+        <v>-0.4052</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3441</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1369</v>
+        <v>0.2187</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1095</v>
+        <v>0.1225</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2464</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>0.9414</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2908</v>
+        <v>-3.1023</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3935</v>
+        <v>-2.1472</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8973</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3662</v>
+        <v>-4.7887</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6785</v>
+        <v>-5.2198</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6877</v>
+        <v>0.4311</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.379</v>
+        <v>-2.4424</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-2.47</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6869</v>
+        <v>0.0276</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9872</v>
+        <v>-2.3463</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.9864</v>
+        <v>-2.7498</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0008</v>
+        <v>0.4035</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9712</v>
+        <v>-0.2821</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3617</v>
+        <v>-0.5831</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6095</v>
+        <v>0.301</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6093</v>
+        <v>1.7731</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>2.0503</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,235 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-6.4765</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.4426</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-4.0338</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.7768</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.913</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.8638</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.4924</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.3502</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-2.4055</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.9447</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.1369</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.2464</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P. RAMOS SAINZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-7.2908</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.3935</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.8973</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.3662</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.6785</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.6877</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.379</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.6919999999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.6869</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.9872</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.9864</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.9712</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.3617</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.6095</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484352_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-25.4393</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>-8.270200000000001</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F27" t="n">
         <v>-17.169</v>
       </c>
-      <c r="G25" t="n">
-        <v>-15.6296</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G27" t="n">
+        <v>-15.6297</v>
+      </c>
+      <c r="H27" t="n">
         <v>-12.9293</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>-2.7005</v>
       </c>
-      <c r="J25" t="n">
-        <v>4.9411</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.937099999999999</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.003900000000000348</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="J27" t="n">
+        <v>4.941100000000002</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.937200000000001</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.003900000000000015</v>
+      </c>
+      <c r="M27" t="n">
         <v>-20.5707</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>-17.8663</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>-2.7043</v>
       </c>
-      <c r="P25" t="n">
-        <v>-9.767099999999999</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="P27" t="n">
+        <v>-9.767100000000001</v>
+      </c>
+      <c r="Q27" t="n">
         <v>-17.5809</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>7.8138</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>-3.9758</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>-2.7777</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>-1.198</v>
       </c>
-      <c r="V25" t="n">
-        <v>3.9331</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="V27" t="n">
+        <v>3.933099999999999</v>
+      </c>
+      <c r="W27" t="n">
         <v>7.146999999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-3.2139</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
